--- a/Result/profitability/7818.xlsx
+++ b/Result/profitability/7818.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM11"/>
+  <dimension ref="A1:AM12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1827,6 +1827,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7818</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2195</v>
+      </c>
+      <c r="E12" t="n">
+        <v>811</v>
+      </c>
+      <c r="F12" t="n">
+        <v>26.98</v>
+      </c>
+      <c r="G12" t="n">
+        <v>87</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2.90%</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>110</v>
+      </c>
+      <c r="J12" t="n">
+        <v>198</v>
+      </c>
+      <c r="K12" t="n">
+        <v>123</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.35375</v>
+      </c>
+      <c r="N12" t="n">
+        <v>29.8075</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-1.989999999999998</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.06869175008629613</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>4.133333333333334</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-3.309999999999999</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.1092769891053152</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK12" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
